--- a/output/graficos_regionales/plot_regional_serie_i_ingr_a_2023_atacama.xlsx
+++ b/output/graficos_regionales/plot_regional_serie_i_ingr_a_2023_atacama.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 16:35</t>
+    <t xml:space="preserve">2026-10-05 01:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -467,10 +467,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>898577.12</v>
+        <v>898577.13</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>812081.12</v>
+        <v>812081.13</v>
       </c>
     </row>
     <row r="3">
@@ -525,7 +525,7 @@
         <v>1315357.25</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1190492.62</v>
+        <v>1190492.63</v>
       </c>
     </row>
     <row r="8">
